--- a/testing/reports/security_e2e_testing.xlsx
+++ b/testing/reports/security_e2e_testing.xlsx
@@ -666,7 +666,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 10:03:46   |   Suites: Unauthenticated Refusal · JWT Validation · IDOR isolation</t>
+          <t>Generated: 2026-07-23 09:12:22   |   Suites: Unauthenticated Refusal · JWT Validation · IDOR isolation</t>
         </is>
       </c>
     </row>
